--- a/artfynd/A 38989-2023 artfynd.xlsx
+++ b/artfynd/A 38989-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38989-2023 artfynd.xlsx
+++ b/artfynd/A 38989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112183478</v>
+        <v>112183475</v>
       </c>
       <c r="B2" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813010</v>
+        <v>813204</v>
       </c>
       <c r="R2" t="n">
-        <v>7426494</v>
+        <v>7426367</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112182677</v>
+        <v>112183477</v>
       </c>
       <c r="B3" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812995</v>
+        <v>813084</v>
       </c>
       <c r="R3" t="n">
-        <v>7426418</v>
+        <v>7426462</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112182826</v>
+        <v>112183478</v>
       </c>
       <c r="B4" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812993</v>
+        <v>813010</v>
       </c>
       <c r="R4" t="n">
-        <v>7426414</v>
+        <v>7426493</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112182679</v>
+        <v>112182677</v>
       </c>
       <c r="B5" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>813003</v>
+        <v>812995</v>
       </c>
       <c r="R5" t="n">
-        <v>7426498</v>
+        <v>7426417</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112183328</v>
+        <v>112182679</v>
       </c>
       <c r="B6" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812999</v>
+        <v>813003</v>
       </c>
       <c r="R6" t="n">
-        <v>7426414</v>
+        <v>7426497</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112183029</v>
+        <v>112182826</v>
       </c>
       <c r="B7" t="n">
-        <v>88219</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>812978</v>
+        <v>812993</v>
       </c>
       <c r="R7" t="n">
-        <v>7426402</v>
+        <v>7426414</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112183027</v>
+        <v>112183328</v>
       </c>
       <c r="B8" t="n">
-        <v>88219</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,7 +1350,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813027</v>
+        <v>812999</v>
       </c>
       <c r="R8" t="n">
         <v>7426414</v>
@@ -1452,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112183475</v>
+        <v>112183027</v>
       </c>
       <c r="B9" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813204</v>
+        <v>813027</v>
       </c>
       <c r="R9" t="n">
-        <v>7426367</v>
+        <v>7426414</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1560,6 +1520,112 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112183029</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torasjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>812978</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7426402</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38989-2023 artfynd.xlsx
+++ b/artfynd/A 38989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183478</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182677</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182679</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183328</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183027</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,8 +1671,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183029</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>